--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,56 +1139,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106193619</v>
+        <v>136548620</v>
       </c>
       <c r="B6" t="n">
-        <v>57966</v>
+        <v>99259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gravfiskbäcken, Hjd</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408055</v>
+        <v>410422</v>
       </c>
       <c r="R6" t="n">
-        <v>6961026</v>
+        <v>6968590</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,12 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,27 +1224,31 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106193619</t>
+          <t>https://artportalen.se/Sighting/136548620</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109952831</v>
+        <v>136537819</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>108105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,45 +1256,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219933</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gravfisktjärn, Hjd</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408068</v>
+        <v>410405</v>
       </c>
       <c r="R7" t="n">
-        <v>6960934</v>
+        <v>6968569</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,12 +1310,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,36 +1326,35 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109952831</t>
+          <t>https://artportalen.se/Sighting/136537819</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127501290</v>
+        <v>136548637</v>
       </c>
       <c r="B8" t="n">
-        <v>102464</v>
+        <v>102694</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,14 +1382,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stornäset, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472338</v>
+        <v>410281</v>
       </c>
       <c r="R8" t="n">
-        <v>6935487</v>
+        <v>6968519</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,22 +1406,22 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,12 +1436,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karolin Ring</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1464,16 +1451,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127501290</t>
+          <t>https://artportalen.se/Sighting/136548637</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16755433</v>
+        <v>136537254</v>
       </c>
       <c r="B9" t="n">
-        <v>79406</v>
+        <v>102694</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,37 +1468,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>221343</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flöten, V delen, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477328</v>
+        <v>410118</v>
       </c>
       <c r="R9" t="n">
-        <v>6933128</v>
+        <v>6968515</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,22 +1512,22 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-07-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-07-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,41 +1538,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Myrkant</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Senvuxen gran</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16755433</t>
+          <t>https://artportalen.se/Sighting/136537254</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122570040</v>
+        <v>136548889</v>
       </c>
       <c r="B10" t="n">
-        <v>79406</v>
+        <v>102694</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,37 +1574,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>221343</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nordkölen, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477323</v>
+        <v>410184</v>
       </c>
       <c r="R10" t="n">
-        <v>6933131</v>
+        <v>6968514</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,32 +1618,22 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,70 +1648,69 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122570040</t>
+          <t>https://artportalen.se/Sighting/136548889</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16755341</v>
+        <v>136548965</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>102694</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221343</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flöten, V delen, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477328</v>
+        <v>410190</v>
       </c>
       <c r="R11" t="n">
-        <v>6933128</v>
+        <v>6968514</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,22 +1724,22 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2014-07-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2014-07-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,79 +1750,73 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Myrkant</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Senvuxen gran</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16755341</t>
+          <t>https://artportalen.se/Sighting/136548965</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570083</v>
+        <v>136548996</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>102694</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221343</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nordkölen, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477336</v>
+        <v>410193</v>
       </c>
       <c r="R12" t="n">
-        <v>6933132</v>
+        <v>6968514</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,32 +1830,22 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,27 +1860,31 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Mats Williamson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122570083</t>
+          <t>https://artportalen.se/Sighting/136548996</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6216343</v>
+        <v>136548665</v>
       </c>
       <c r="B13" t="n">
-        <v>97985</v>
+        <v>108367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,37 +1892,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224363</v>
+        <v>220083</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nordkölen SV Lillberget, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476981</v>
+        <v>394961</v>
       </c>
       <c r="R13" t="n">
-        <v>6932808</v>
+        <v>6966540</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,27 +1936,22 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1998-07-18</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1998-07-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>taxyta S1480</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,36 +1962,35 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>hygge</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6216343</t>
+          <t>https://artportalen.se/Sighting/136548665</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6228090</v>
+        <v>136537429</v>
       </c>
       <c r="B14" t="n">
-        <v>97987</v>
+        <v>99344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,37 +1998,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224364</v>
+        <v>219811</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nordkölen S Lillberget, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477361</v>
+        <v>396376</v>
       </c>
       <c r="R14" t="n">
-        <v>6932812</v>
+        <v>6966047</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,27 +2042,22 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1998-07-18</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1998-07-18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>taxyta S1100</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,90 +2068,73 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>brukningsväg (fd)</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6228090</t>
+          <t>https://artportalen.se/Sighting/136537429</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89087231</v>
+        <v>136537498</v>
       </c>
       <c r="B15" t="n">
-        <v>57864</v>
+        <v>99344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100011</v>
+        <v>219811</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flarken,Nybodarna, Ljungan, Rätan, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475745</v>
+        <v>396393</v>
       </c>
       <c r="R15" t="n">
-        <v>6930037</v>
+        <v>6966046</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2218,27 +2148,22 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äter på slaktplats av älg.</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,16 +2178,1999 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537498</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136537602</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99344</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>396417</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6966044</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537602</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136537906</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99344</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>396492</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966032</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537906</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136537612</v>
+      </c>
+      <c r="B18" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>396405</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966041</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537612</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136537928</v>
+      </c>
+      <c r="B19" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>396521</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966025</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537928</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136541377</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99344</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>397840</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6965717</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136541377</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136547479</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99344</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>397858</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6965717</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136547479</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136541238</v>
+      </c>
+      <c r="B22" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>397949</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6965718</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136541238</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136548950</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Z535 Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>397862</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6965717</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136548950</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>106193619</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gravfiskbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>408055</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6961026</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-01-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-01-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Stefan Dahlsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Stefan Dahlsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106193619</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>109952831</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gravfisktjärn, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>408068</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6960934</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Stefan Dahlsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Stefan Dahlsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109952831</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127501290</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stornäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>472338</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6935487</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127501290</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>16755433</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79406</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>864</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Flöten, V delen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>477328</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6933128</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2014-07-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2014-07-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Myrkant</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16755433</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122570040</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79406</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>864</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>477323</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6933131</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570040</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16755341</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Flöten, V delen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>477328</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6933128</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2014-07-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2014-07-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Myrkant</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16755341</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122570083</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>477336</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6933132</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570083</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6216343</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nordkölen SV Lillberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>476981</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6932808</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>1998-07-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1998-07-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>taxyta S1480</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6216343</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6228090</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nordkölen S Lillberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>477361</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6932812</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1998-07-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1998-07-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>taxyta S1100</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>brukningsväg (fd)</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6228090</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>89087231</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flarken,Nybodarna, Ljungan, Rätan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>475745</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6930037</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-11-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-11-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äter på slaktplats av älg.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
           <t>Håkan Carlsson</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>Håkan Carlsson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr">
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89087231</t>
         </is>
@@ -2284,6 +4192,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>136548620</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136537819</v>
       </c>
       <c r="B7" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136548637</v>
       </c>
       <c r="B8" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136537254</v>
       </c>
       <c r="B9" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>136548889</v>
       </c>
       <c r="B10" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136548965</v>
       </c>
       <c r="B11" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>136548996</v>
       </c>
       <c r="B12" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>136548665</v>
       </c>
       <c r="B13" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>136537429</v>
       </c>
       <c r="B14" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>136537498</v>
       </c>
       <c r="B15" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136537602</v>
       </c>
       <c r="B16" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>136537906</v>
       </c>
       <c r="B17" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136537612</v>
       </c>
       <c r="B18" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>136537928</v>
       </c>
       <c r="B19" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136541377</v>
       </c>
       <c r="B20" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136547479</v>
       </c>
       <c r="B21" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136541238</v>
       </c>
       <c r="B22" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>136548950</v>
       </c>
       <c r="B23" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>136548620</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136537819</v>
       </c>
       <c r="B7" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136548637</v>
       </c>
       <c r="B8" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136537254</v>
       </c>
       <c r="B9" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>136548889</v>
       </c>
       <c r="B10" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136548965</v>
       </c>
       <c r="B11" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>136548996</v>
       </c>
       <c r="B12" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>136548665</v>
       </c>
       <c r="B13" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>136537429</v>
       </c>
       <c r="B14" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>136537498</v>
       </c>
       <c r="B15" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136537602</v>
       </c>
       <c r="B16" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>136537906</v>
       </c>
       <c r="B17" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136537612</v>
       </c>
       <c r="B18" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>136537928</v>
       </c>
       <c r="B19" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136541377</v>
       </c>
       <c r="B20" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136547479</v>
       </c>
       <c r="B21" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136541238</v>
       </c>
       <c r="B22" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>136548950</v>
       </c>
       <c r="B23" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>136548620</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136537819</v>
       </c>
       <c r="B7" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136548637</v>
       </c>
       <c r="B8" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136537254</v>
       </c>
       <c r="B9" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>136548889</v>
       </c>
       <c r="B10" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136548965</v>
       </c>
       <c r="B11" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>136548996</v>
       </c>
       <c r="B12" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>136548665</v>
       </c>
       <c r="B13" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>136537429</v>
       </c>
       <c r="B14" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>136537498</v>
       </c>
       <c r="B15" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136537602</v>
       </c>
       <c r="B16" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>136537906</v>
       </c>
       <c r="B17" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136537612</v>
       </c>
       <c r="B18" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>136537928</v>
       </c>
       <c r="B19" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136541377</v>
       </c>
       <c r="B20" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136547479</v>
       </c>
       <c r="B21" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136541238</v>
       </c>
       <c r="B22" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>136548950</v>
       </c>
       <c r="B23" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>136548620</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136537819</v>
       </c>
       <c r="B7" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136548637</v>
       </c>
       <c r="B8" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136537254</v>
       </c>
       <c r="B9" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>136548889</v>
       </c>
       <c r="B10" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136548965</v>
       </c>
       <c r="B11" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>136548996</v>
       </c>
       <c r="B12" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>136548665</v>
       </c>
       <c r="B13" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>136537429</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>136537498</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136537602</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>136537906</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2414,7 +2414,7 @@
         <v>136537612</v>
       </c>
       <c r="B18" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>136537928</v>
       </c>
       <c r="B19" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>136541377</v>
       </c>
       <c r="B20" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>136547479</v>
       </c>
       <c r="B21" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>136541238</v>
       </c>
       <c r="B22" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>136548950</v>
       </c>
       <c r="B23" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16952656</v>
+        <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>93423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Petteravan, Hjd</t>
+          <t>Vikavan, Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415433</v>
+        <v>415693</v>
       </c>
       <c r="R2" t="n">
-        <v>6972118</v>
+        <v>6972075</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-06-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-06-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16952656</t>
+          <t>https://artportalen.se/Sighting/136871746</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16952657</v>
+        <v>136871681</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>58008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Petteravan, Hjd</t>
+          <t>Vikavan, Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415433</v>
+        <v>415694</v>
       </c>
       <c r="R3" t="n">
-        <v>6972118</v>
+        <v>6972075</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-06-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-06-05</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,83 +877,70 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16952657</t>
+          <t>https://artportalen.se/Sighting/136871681</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129793526</v>
+        <v>136871755</v>
       </c>
       <c r="B4" t="n">
-        <v>57141</v>
+        <v>58008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ålderövallen, Ålderövallen, Hjd</t>
+          <t>Vikavan, Vikavan, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404642</v>
+        <v>415695</v>
       </c>
       <c r="R4" t="n">
-        <v>6970346</v>
+        <v>6972074</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,22 +964,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,27 +989,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kent Moén, Eva Moén</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129793526</t>
+          <t>https://artportalen.se/Sighting/136871755</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119497136</v>
+        <v>16952656</v>
       </c>
       <c r="B5" t="n">
-        <v>58114</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,46 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ålderövallen, Hjd</t>
+          <t>Petteravan, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404877</v>
+        <v>415433</v>
       </c>
       <c r="R5" t="n">
-        <v>6970011</v>
+        <v>6972118</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,22 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,65 +1091,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119497136</t>
+          <t>https://artportalen.se/Sighting/16952656</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136548620</v>
+        <v>16952657</v>
       </c>
       <c r="B6" t="n">
-        <v>99270</v>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Z535 Storsjö, Hjd</t>
+          <t>Petteravan, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410422</v>
+        <v>415433</v>
       </c>
       <c r="R6" t="n">
-        <v>6968590</v>
+        <v>6972118</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2014-06-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,31 +1197,31 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136548620</t>
+          <t>https://artportalen.se/Sighting/16952657</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136537819</v>
+        <v>129793526</v>
       </c>
       <c r="B7" t="n">
-        <v>108116</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,37 +1229,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219933</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Z535 Storsjö, Hjd</t>
+          <t>Ålderövallen, Ålderövallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410405</v>
+        <v>404642</v>
       </c>
       <c r="R7" t="n">
-        <v>6968569</v>
+        <v>6970346</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,12 +1297,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,31 +1327,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Kent Moén, Eva Moén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136537819</t>
+          <t>https://artportalen.se/Sighting/129793526</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136548637</v>
+        <v>119497136</v>
       </c>
       <c r="B8" t="n">
-        <v>102705</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,37 +1355,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221343</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Z535 Storsjö, Hjd</t>
+          <t>Ålderövallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410281</v>
+        <v>404877</v>
       </c>
       <c r="R8" t="n">
-        <v>6968519</v>
+        <v>6970011</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,12 +1418,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,53 +1448,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136548637</t>
+          <t>https://artportalen.se/Sighting/119497136</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136537254</v>
+        <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>102705</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221343</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410118</v>
+        <v>410422</v>
       </c>
       <c r="R9" t="n">
-        <v>6968515</v>
+        <v>6968590</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,38 +1565,38 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136537254</t>
+          <t>https://artportalen.se/Sighting/136548620</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136548889</v>
+        <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>102705</v>
+        <v>108116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221343</v>
+        <v>219933</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410184</v>
+        <v>410405</v>
       </c>
       <c r="R10" t="n">
-        <v>6968514</v>
+        <v>6968569</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,12 +1636,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,13 +1671,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136548889</t>
+          <t>https://artportalen.se/Sighting/136537819</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136548965</v>
+        <v>136548637</v>
       </c>
       <c r="B11" t="n">
         <v>102705</v>
@@ -1704,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410190</v>
+        <v>410281</v>
       </c>
       <c r="R11" t="n">
-        <v>6968514</v>
+        <v>6968519</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1769,13 +1777,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136548965</t>
+          <t>https://artportalen.se/Sighting/136548637</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136548996</v>
+        <v>136537254</v>
       </c>
       <c r="B12" t="n">
         <v>102705</v>
@@ -1810,10 +1818,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410193</v>
+        <v>410118</v>
       </c>
       <c r="R12" t="n">
-        <v>6968514</v>
+        <v>6968515</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,38 +1883,38 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136548996</t>
+          <t>https://artportalen.se/Sighting/136537254</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136548665</v>
+        <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>108378</v>
+        <v>102705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220083</v>
+        <v>221343</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1924,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>394961</v>
+        <v>410184</v>
       </c>
       <c r="R13" t="n">
-        <v>6966540</v>
+        <v>6968514</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1981,38 +1989,38 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136548665</t>
+          <t>https://artportalen.se/Sighting/136548889</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136537429</v>
+        <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>99355</v>
+        <v>102705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219811</v>
+        <v>221343</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>396376</v>
+        <v>410190</v>
       </c>
       <c r="R14" t="n">
-        <v>6966047</v>
+        <v>6968514</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2087,38 +2095,38 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136537429</t>
+          <t>https://artportalen.se/Sighting/136548965</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136537498</v>
+        <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>99355</v>
+        <v>102705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219811</v>
+        <v>221343</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>396393</v>
+        <v>410193</v>
       </c>
       <c r="R15" t="n">
-        <v>6966046</v>
+        <v>6968514</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2193,16 +2201,16 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136537498</t>
+          <t>https://artportalen.se/Sighting/136548996</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136537602</v>
+        <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>99355</v>
+        <v>108378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,21 +2218,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219811</v>
+        <v>220083</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2234,10 +2242,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>396417</v>
+        <v>394961</v>
       </c>
       <c r="R16" t="n">
-        <v>6966044</v>
+        <v>6966540</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2299,13 +2307,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136537602</t>
+          <t>https://artportalen.se/Sighting/136548665</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136537906</v>
+        <v>136537429</v>
       </c>
       <c r="B17" t="n">
         <v>99355</v>
@@ -2340,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>396492</v>
+        <v>396376</v>
       </c>
       <c r="R17" t="n">
-        <v>6966032</v>
+        <v>6966047</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2395,7 +2403,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2405,16 +2413,16 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136537906</t>
+          <t>https://artportalen.se/Sighting/136537429</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136537612</v>
+        <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>108378</v>
+        <v>99355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,21 +2430,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220083</v>
+        <v>219811</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2446,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>396405</v>
+        <v>396393</v>
       </c>
       <c r="R18" t="n">
-        <v>6966041</v>
+        <v>6966046</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2511,16 +2519,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136537612</t>
+          <t>https://artportalen.se/Sighting/136537498</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136537928</v>
+        <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>108378</v>
+        <v>99355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,21 +2536,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220083</v>
+        <v>219811</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2560,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>396521</v>
+        <v>396417</v>
       </c>
       <c r="R19" t="n">
-        <v>6966025</v>
+        <v>6966044</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2617,13 +2625,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136537928</t>
+          <t>https://artportalen.se/Sighting/136537602</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136541377</v>
+        <v>136537906</v>
       </c>
       <c r="B20" t="n">
         <v>99355</v>
@@ -2658,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397840</v>
+        <v>396492</v>
       </c>
       <c r="R20" t="n">
-        <v>6965717</v>
+        <v>6966032</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2723,16 +2731,16 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136541377</t>
+          <t>https://artportalen.se/Sighting/136537906</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136547479</v>
+        <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>99355</v>
+        <v>108378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,21 +2748,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219811</v>
+        <v>220083</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2764,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397858</v>
+        <v>396405</v>
       </c>
       <c r="R21" t="n">
-        <v>6965717</v>
+        <v>6966041</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2829,13 +2837,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136547479</t>
+          <t>https://artportalen.se/Sighting/136537612</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136541238</v>
+        <v>136537928</v>
       </c>
       <c r="B22" t="n">
         <v>108378</v>
@@ -2870,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397949</v>
+        <v>396521</v>
       </c>
       <c r="R22" t="n">
-        <v>6965718</v>
+        <v>6966025</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2935,16 +2943,16 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136541238</t>
+          <t>https://artportalen.se/Sighting/136537928</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136548950</v>
+        <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>108378</v>
+        <v>99355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2952,21 +2960,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220083</v>
+        <v>219811</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,7 +2984,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>397862</v>
+        <v>397840</v>
       </c>
       <c r="R23" t="n">
         <v>6965717</v>
@@ -3041,62 +3049,54 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136548950</t>
+          <t>https://artportalen.se/Sighting/136541377</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106193619</v>
+        <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>57966</v>
+        <v>99355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100048</v>
+        <v>219811</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gravfiskbäcken, Hjd</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408055</v>
+        <v>397858</v>
       </c>
       <c r="R24" t="n">
-        <v>6961026</v>
+        <v>6965717</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3140,27 +3140,31 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106193619</t>
+          <t>https://artportalen.se/Sighting/136547479</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109952831</v>
+        <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>57950</v>
+        <v>108378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3168,45 +3172,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220083</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gravfisktjärn, Hjd</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408068</v>
+        <v>397949</v>
       </c>
       <c r="R25" t="n">
-        <v>6960934</v>
+        <v>6965718</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3230,12 +3226,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,71 +3242,70 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109952831</t>
+          <t>https://artportalen.se/Sighting/136541238</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127501290</v>
+        <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>102464</v>
+        <v>108378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221343</v>
+        <v>220083</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stornäset, Jmt</t>
+          <t>Z535 Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472338</v>
+        <v>397862</v>
       </c>
       <c r="R26" t="n">
-        <v>6935487</v>
+        <v>6965717</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3327,22 +3322,22 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,12 +3352,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Staffan Fridh</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karolin Ring</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3372,16 +3367,16 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127501290</t>
+          <t>https://artportalen.se/Sighting/136548950</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16755433</v>
+        <v>106193619</v>
       </c>
       <c r="B27" t="n">
-        <v>79406</v>
+        <v>57966</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3389,37 +3384,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>100048</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Flöten, V delen, Jmt</t>
+          <t>Gravfiskbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477328</v>
+        <v>408055</v>
       </c>
       <c r="R27" t="n">
-        <v>6933128</v>
+        <v>6961026</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3433,22 +3436,22 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2014-07-29</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2014-07-29</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,76 +3462,74 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Myrkant</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Senvuxen gran</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16755433</t>
+          <t>https://artportalen.se/Sighting/106193619</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570040</v>
+        <v>109952831</v>
       </c>
       <c r="B28" t="n">
-        <v>79406</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nordkölen, Jmt</t>
+          <t>Gravfisktjärn, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477323</v>
+        <v>408068</v>
       </c>
       <c r="R28" t="n">
-        <v>6933131</v>
+        <v>6960934</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3545,32 +3546,22 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Rätan</t>
+          <t>Storsjö</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3581,74 +3572,74 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Mats Williamson</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122570040</t>
+          <t>https://artportalen.se/Sighting/109952831</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16755341</v>
+        <v>127501290</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>102464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221343</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Flöten, V delen, Jmt</t>
+          <t>Stornäset, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477328</v>
+        <v>472338</v>
       </c>
       <c r="R29" t="n">
-        <v>6933128</v>
+        <v>6935487</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3672,12 +3663,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2014-07-29</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2014-07-29</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3688,76 +3679,70 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Myrkant</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Senvuxen gran</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16755341</t>
+          <t>https://artportalen.se/Sighting/127501290</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122570083</v>
+        <v>16755433</v>
       </c>
       <c r="B30" t="n">
-        <v>79327</v>
+        <v>79406</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nordkölen, Jmt</t>
+          <t>Flöten, V delen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477336</v>
+        <v>477328</v>
       </c>
       <c r="R30" t="n">
-        <v>6933132</v>
+        <v>6933128</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3784,22 +3769,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2014-07-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2014-07-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3810,66 +3785,76 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Myrkant</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Senvuxen gran</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Mats Williamson</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122570083</t>
+          <t>https://artportalen.se/Sighting/16755433</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6216343</v>
+        <v>122570040</v>
       </c>
       <c r="B31" t="n">
-        <v>97985</v>
+        <v>79406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>224363</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Nordkölen SV Lillberget, Jmt</t>
+          <t>Nordkölen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476981</v>
+        <v>477323</v>
       </c>
       <c r="R31" t="n">
-        <v>6932808</v>
+        <v>6933131</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3896,17 +3881,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1998-07-18</t>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1998-07-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>taxyta S1480</t>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3917,71 +3907,71 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>hygge</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Via Mats Williamson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6216343</t>
+          <t>https://artportalen.se/Sighting/122570040</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6228090</v>
+        <v>16755341</v>
       </c>
       <c r="B32" t="n">
-        <v>97987</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nordkölen S Lillberget, Jmt</t>
+          <t>Flöten, V delen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477361</v>
+        <v>477328</v>
       </c>
       <c r="R32" t="n">
-        <v>6932812</v>
+        <v>6933128</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4008,17 +3998,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1998-07-18</t>
+          <t>2014-07-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1998-07-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>taxyta S1100</t>
+          <t>2014-07-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4032,87 +4017,76 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>brukningsväg (fd)</t>
+          <t>Myrkant</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Senvuxen gran</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6228090</t>
+          <t>https://artportalen.se/Sighting/16755341</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89087231</v>
+        <v>122570083</v>
       </c>
       <c r="B33" t="n">
-        <v>57864</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100011</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flarken,Nybodarna, Ljungan, Rätan, Jmt</t>
+          <t>Nordkölen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475745</v>
+        <v>477336</v>
       </c>
       <c r="R33" t="n">
-        <v>6930037</v>
+        <v>6933132</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4136,17 +4110,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äter på slaktplats av älg.</t>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,16 +4140,363 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Carlsson</t>
+          <t>Mats Williamson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Carlsson</t>
+          <t>Via Mats Williamson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570083</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6216343</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nordkölen SV Lillberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>476981</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6932808</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>1998-07-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>1998-07-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>taxyta S1480</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6216343</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6228090</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nordkölen S Lillberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>477361</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6932812</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>1998-07-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1998-07-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>taxyta S1100</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>brukningsväg (fd)</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6228090</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>89087231</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Flarken,Nybodarna, Ljungan, Rätan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>475745</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6930037</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-11-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-11-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äter på slaktplats av älg.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89087231</t>
         </is>
@@ -4210,6 +4536,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -2297,7 +2297,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson</t>
+          <t>Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136871681</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136871755</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136871681</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136871755</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136548620</v>
       </c>
       <c r="B9" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>136537819</v>
       </c>
       <c r="B10" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>136548637</v>
       </c>
       <c r="B11" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>136537254</v>
       </c>
       <c r="B12" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136548889</v>
       </c>
       <c r="B13" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>136548965</v>
       </c>
       <c r="B14" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>136548996</v>
       </c>
       <c r="B15" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>136548665</v>
       </c>
       <c r="B16" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>136537429</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136537498</v>
       </c>
       <c r="B18" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136537602</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136537906</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136537612</v>
       </c>
       <c r="B21" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>136537928</v>
       </c>
       <c r="B22" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>136541377</v>
       </c>
       <c r="B23" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>136547479</v>
       </c>
       <c r="B24" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136541238</v>
       </c>
       <c r="B25" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>136548950</v>
       </c>
       <c r="B26" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -811,11 +811,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vikavan, Vikavan, Hjd</t>
@@ -923,11 +919,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vikavan, Vikavan, Hjd</t>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136871681</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136871755</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136871681</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136871755</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136871681</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>136871755</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 293-2024 artfynd.xlsx
+++ b/artfynd/S 293-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136871746</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
